--- a/public/abc2/material/gastro-pedidos.xlsx
+++ b/public/abc2/material/gastro-pedidos.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Hora</v>
       </c>
       <c r="B1" t="str">
-        <v>Cliente</v>
+        <v>Cliente/Mesa</v>
       </c>
       <c r="C1" t="str">
         <v>Pedido</v>
@@ -418,75 +418,687 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>20:15</v>
+        <v>20:00</v>
       </c>
       <c r="B2" t="str">
-        <v>Mesa 4</v>
+        <v>Mesa 1</v>
       </c>
       <c r="C2" t="str">
-        <v>2 muzzarella, 1 napolitana</v>
+        <v>1 muzzarella</v>
       </c>
       <c r="D2" t="str">
-        <v>En horno</v>
+        <v>Pedido</v>
       </c>
       <c r="E2">
-        <v>18500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>20:22</v>
+        <v>20:07</v>
       </c>
       <c r="B3" t="str">
-        <v>Delivery - Juan</v>
+        <v>Mesa 2</v>
       </c>
       <c r="C3" t="str">
-        <v>1 especial, 6 empanadas</v>
+        <v>1 napolitana</v>
       </c>
       <c r="D3" t="str">
-        <v>En camino</v>
+        <v>En horno</v>
       </c>
       <c r="E3">
-        <v>14200</v>
+        <v>19700</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>20:30</v>
+        <v>20:14</v>
       </c>
       <c r="B4" t="str">
-        <v>Mostrador</v>
+        <v>Mesa 3</v>
       </c>
       <c r="C4" t="str">
-        <v>1 fugazzeta, gaseosa</v>
+        <v>1 fugazzeta</v>
       </c>
       <c r="D4" t="str">
         <v>Listo</v>
       </c>
       <c r="E4">
-        <v>9800</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>20:41</v>
+        <v>20:21</v>
       </c>
       <c r="B5" t="str">
-        <v>Mesa 7</v>
+        <v>Mesa 4</v>
       </c>
       <c r="C5" t="str">
-        <v>3 comunes, 2 cervezas</v>
+        <v>1 especial</v>
       </c>
       <c r="D5" t="str">
-        <v>Tomando</v>
+        <v>Entregado</v>
       </c>
       <c r="E5">
-        <v>22000</v>
+        <v>25100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>20:28</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mesa 5</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2 comunes</v>
+      </c>
+      <c r="D6" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E6">
+        <v>18800</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>20:35</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Delivery - Juan</v>
+      </c>
+      <c r="C7" t="str">
+        <v>6 empanadas</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E7">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>20:42</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Delivery - Ana</v>
+      </c>
+      <c r="C8" t="str">
+        <v>12 empanadas</v>
+      </c>
+      <c r="D8" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E8">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>20:49</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Delivery - Pedro</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1 docena empanadas + gaseosa</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E9">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>20:56</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mostrador</v>
+      </c>
+      <c r="C10" t="str">
+        <v>papas fritas</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E10">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>20:03</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Take away</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2 muzzarellas + gaseosa</v>
+      </c>
+      <c r="D11" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E11">
+        <v>23300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>20:10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Mesa 1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>1 muzzarella</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E12">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>20:17</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mesa 2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>1 napolitana</v>
+      </c>
+      <c r="D13" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E13">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>21:24</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Mesa 3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>1 fugazzeta</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E14">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>21:31</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Mesa 4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>1 especial</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E15">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>21:38</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Mesa 5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2 comunes</v>
+      </c>
+      <c r="D16" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E16">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>21:45</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Delivery - Juan</v>
+      </c>
+      <c r="C17" t="str">
+        <v>6 empanadas</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E17">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>21:52</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Delivery - Ana</v>
+      </c>
+      <c r="C18" t="str">
+        <v>12 empanadas</v>
+      </c>
+      <c r="D18" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E18">
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>21:59</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Delivery - Pedro</v>
+      </c>
+      <c r="C19" t="str">
+        <v>1 docena empanadas + gaseosa</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E19">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>21:06</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mostrador</v>
+      </c>
+      <c r="C20" t="str">
+        <v>papas fritas</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E20">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>21:13</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Take away</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2 muzzarellas + gaseosa</v>
+      </c>
+      <c r="D21" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E21">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>21:20</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Mesa 1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>1 muzzarella</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E22">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>21:27</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Mesa 2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>1 napolitana</v>
+      </c>
+      <c r="D23" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E23">
+        <v>19700</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>21:34</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Mesa 3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>1 fugazzeta</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E24">
+        <v>13400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>21:41</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Mesa 4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>1 especial</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E25">
+        <v>25100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>22:48</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Mesa 5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2 comunes</v>
+      </c>
+      <c r="D26" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E26">
+        <v>18800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>22:55</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Delivery - Juan</v>
+      </c>
+      <c r="C27" t="str">
+        <v>6 empanadas</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E27">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>22:02</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Delivery - Ana</v>
+      </c>
+      <c r="C28" t="str">
+        <v>12 empanadas</v>
+      </c>
+      <c r="D28" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E28">
+        <v>24200</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>22:09</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Delivery - Pedro</v>
+      </c>
+      <c r="C29" t="str">
+        <v>1 docena empanadas + gaseosa</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E29">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>22:16</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Mostrador</v>
+      </c>
+      <c r="C30" t="str">
+        <v>papas fritas</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E30">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>22:23</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Take away</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2 muzzarellas + gaseosa</v>
+      </c>
+      <c r="D31" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E31">
+        <v>23300</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>22:30</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Mesa 1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>1 muzzarella</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E32">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>22:37</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Mesa 2</v>
+      </c>
+      <c r="C33" t="str">
+        <v>1 napolitana</v>
+      </c>
+      <c r="D33" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E33">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>22:44</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Mesa 3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>1 fugazzeta</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E34">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>22:51</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Mesa 4</v>
+      </c>
+      <c r="C35" t="str">
+        <v>1 especial</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E35">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>22:58</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Mesa 5</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2 comunes</v>
+      </c>
+      <c r="D36" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E36">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>22:05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Delivery - Juan</v>
+      </c>
+      <c r="C37" t="str">
+        <v>6 empanadas</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Pedido</v>
+      </c>
+      <c r="E37">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>23:12</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Delivery - Ana</v>
+      </c>
+      <c r="C38" t="str">
+        <v>12 empanadas</v>
+      </c>
+      <c r="D38" t="str">
+        <v>En horno</v>
+      </c>
+      <c r="E38">
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>23:19</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Delivery - Pedro</v>
+      </c>
+      <c r="C39" t="str">
+        <v>1 docena empanadas + gaseosa</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="E39">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>23:26</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Mostrador</v>
+      </c>
+      <c r="C40" t="str">
+        <v>papas fritas</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Entregado</v>
+      </c>
+      <c r="E40">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>23:33</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Take away</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2 muzzarellas + gaseosa</v>
+      </c>
+      <c r="D41" t="str">
+        <v>En camino</v>
+      </c>
+      <c r="E41">
+        <v>14300</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
   </ignoredErrors>
 </worksheet>
 </file>